--- a/光伏配储项目/电价数据/2026/鸭涌河站.xlsx
+++ b/光伏配储项目/电价数据/2026/鸭涌河站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55361</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.51879</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.86185</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.12632</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.02035</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.91898</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.7198</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.72922</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.5388999999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.59109</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.52449</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.69172</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.6918500000000001</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.6822999999999999</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.51778</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.70925</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.69969</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.68832</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.5276799999999999</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.7024600000000001</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.54659</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.70055</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.7083200000000001</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.55192</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.73333</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.82277</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.85825</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.67679</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.67195</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.73391</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.75663</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.01015</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.99463</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.08555</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7504400000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.6980299999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50116</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.78359</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.95001</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31252</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.5230900000000001</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.75991</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76781</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74753</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.92825</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.89478</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04803</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.31531</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.12364</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.12255</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7341599999999999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.21043</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.16911</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09676</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22876</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53483</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.10547</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.2475</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47632</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.30524</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23612</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.79973</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.41067</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35418</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28486</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.1682</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03709</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17646</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5126000000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.6144500000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.5147</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.58877</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.49352</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48682</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.52343</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.50456</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.51467</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.51463</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.50457</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.55968</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.76952</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.07438</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8401799999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.59214</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48581</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.53906</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45888</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.5093799999999999</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.93516</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.15089</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.1198</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03768</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.98702</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.70787</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5479299999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.56689</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6797300000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.15408</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.2312</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47528</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15839</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.62936</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.07852</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.81817</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.25127</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.1361</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28321</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62166</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.6384099999999999</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57013</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62193</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.16119</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16854</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17719</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17173</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.96853</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18755</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20237</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19405</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66891</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.1617</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20559</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.21084</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50716</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.41233</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16796</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50943</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26399</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7432000000000001</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7648200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9153300000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.60361</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.68575</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6948200000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.57833</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.8436</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.59797</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.58997</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.5584199999999999</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.55838</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.63585</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48823</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.5857899999999999</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48874</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.5762999999999999</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.52436</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.55787</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.51291</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.49938</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.50936</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.46267</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.69286</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83075</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10797</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.8737999999999999</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7449199999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70317</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6044400000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64289</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.72921</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16441</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.52201</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6770900000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16694</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.62132</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18773</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.16527</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.79286</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.93979</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16418</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.16559</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8922599999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5595</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47465</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67425</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16558</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02854</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.16469</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.39303</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23606</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16595</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21571</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20945</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.40158</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.2689</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28583</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64854</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.17168</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17441</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78432</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03919</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07846</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09933</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.0854</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20466</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16826</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24848</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.99505</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75434</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.7109</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5302100000000001</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.11008</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.72278</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.71575</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.20593</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6811499999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.85515</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.5415399999999999</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.61394</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.23164</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.5945</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.52549</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.65612</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.5882200000000001</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.52858</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.5180900000000001</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.5116499999999999</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.45843</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.51073</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.52289</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.5789299999999999</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.49643</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.49537</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.4605</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48998</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6763899999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.71829</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9327000000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16785</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30917</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.83808</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55155</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66583</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90362</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.86473</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16403</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43974</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77261</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.95333</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20503</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.6892</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12235</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52242</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48524</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6542899999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.99621</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10263</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24909</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16855</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.06124</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.98189</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02571</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.98966</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.25191</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.4412</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.79314</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.3487</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.23565</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.19134</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.84763</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07419</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.16094</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12157</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.1541</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.2548</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31823</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15413</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.2696</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18775</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18603</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.1886</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18932</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17483</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.15239</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72394</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7262000000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32162</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74363</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50454</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52299</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45547</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42585</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45474</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.7164299999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.84773</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61478</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70162</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.7266699999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8452799999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70511</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55071</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54975</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5384800000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.5923200000000001</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47057</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08537</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.54992</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51217</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6332300000000001</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.50224</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48309</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48324</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48738</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.5943099999999999</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50584</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3439</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.19103</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9660599999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.98189</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5902999999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.64781</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.5463</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.52962</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.54514</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.51436</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.51312</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.68865</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.5287000000000001</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.52901</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.5118199999999999</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.5134</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07335999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04535</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08283</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12871</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04697</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04591</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04665</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27666</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.59377</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.54018</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.5619400000000001</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.54198</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55777</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27008</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7417100000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8744299999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.67472</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6486900000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.66755</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7486</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.93945</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48069</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.72999</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73168</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.88795</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.6316799999999999</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5358200000000001</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48251</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08548</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73164</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72829</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.63881</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6029600000000001</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.72854</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.78867</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78273</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6003999999999999</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.74175</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01808</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40622</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.84315</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.434</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29786</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.78875</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.3807</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04504</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.40097</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76538</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44399</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7744</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8003899999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78504</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8787999999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50198</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41139</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46011</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2185</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54123</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.6170599999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.5847100000000001</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.56512</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.57365</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.58023</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.50864</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.58175</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.5616100000000001</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.4700299999999999</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.48133</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.54313</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.5153799999999999</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.5189600000000001</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.51559</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.5155700000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.5509400000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.51655</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.56694</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.57299</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.49303</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56368</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66623</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07967</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6385700000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5026700000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5692699999999999</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59868</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00142</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30664</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27477</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55925</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8017300000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6508700000000001</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55061</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.95648</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7766000000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7257</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64215</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57539</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.98909</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.93233</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78908</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5423300000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.6715</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.58976</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.67111</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.62273</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.66361</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.70504</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.64098</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.66226</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58328</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.57784</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.6603</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.67708</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.62342</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.67086</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.68909</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7613300000000001</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.67988</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.75828</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.68899</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.68672</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.68825</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.67252</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.6622400000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.62053</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.6614099999999999</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.6049600000000001</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.54426</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.60809</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.55677</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5813700000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.55823</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.54369</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.5334500000000001</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46938</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57623</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.6103200000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6234400000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.68137</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5357799999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.50104</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.52562</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.49303</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64179</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51314</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.61771</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7278</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.87146</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.1118</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.93216</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5450900000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11341</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84373</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9494400000000001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.85936</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.6397699999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.80988</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06754</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.57033</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52246</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.8751599999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.99575</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.54222</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.19082</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.78385</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.81349</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.74137</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.73983</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40405</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47514</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19615</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51263</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7931900000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.74913</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16615</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92144</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.6431699999999999</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.66814</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.70078</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55504</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16406</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61246</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9092899999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5769299999999999</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.5745</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.33648</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.26099</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.2288</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.34328</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.00825</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.5191</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6021299999999999</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8590399999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50583</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7503099999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07582</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07377</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9065299999999999</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.98285</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.93649</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17406</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15432</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8625900000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15559</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60772</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.97063</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01585</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.15501</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9504900000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.99076</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58473</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.92423</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.98153</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.08908</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.88562</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.87325</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79355</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09658</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55597</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.96004</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.99138</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74333</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33174</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.6090800000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.49186</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.49496</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.5075500000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.55067</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.59275</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.50101</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.48109</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.48988</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.53295</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8330700000000001</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71436</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.55079</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.5685800000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.73072</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.8607899999999999</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.57075</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.57485</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.57662</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.51145</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.51122</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.5588</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.61897</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.56269</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.57065</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.46037</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.46273</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6772699999999999</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5427000000000001</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.51305</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50658</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.50996</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56829</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.44882</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.5731799999999999</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.5297999999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.53634</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.52362</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.55015</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.5159199999999999</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.50319</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.52427</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.52507</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.48634</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.47379</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55413</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7012200000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6029600000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6276900000000001</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27147</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16639</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8522000000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45078</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70141</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.94024</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16796</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12166</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01854</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54187</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44601</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5632200000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.46282</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.50493</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.44201</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.48564</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.50969</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.5085500000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.58088</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.7236</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.06102</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.11403</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.99121</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.97993</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98148</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56583</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54722</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94628</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08621</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78431</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01323</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76831</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64888</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64162</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70892</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29845</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.7886</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.3783</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.51133</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.17282</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.99946</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.66774</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62432</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65796</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67133</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.6664</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64338</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66787</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20688</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70079</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78259</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.6981</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70588</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71404</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63356</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74833</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02167</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13145</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69194</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70038</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69415</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77378</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72394</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.81332</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6666599999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46308</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.06622</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.58078</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.49053</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34415</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.6007400000000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17753</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.47784</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.5027</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.49141</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.46453</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.5112099999999999</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.5032</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.4982200000000001</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.45672</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.44387</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.74721</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49507</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51078</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51902</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40657</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92253</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47498</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17992</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90225</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76319</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4976</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48995</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74681</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51516</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.6813</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45384</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.6648099999999999</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6517999999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.52437</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48943</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.48451</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.7073400000000001</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.47281</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.44205</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43921</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51644</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54603</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76148</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7681699999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48001</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54657</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50161</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72312</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7626000000000001</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55424</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50184</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02053</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.4872</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44688</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09486</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12981</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08376</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11235</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12882</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01862</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19441</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14268</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13188</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17435</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84139</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19129</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84845</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34117</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9037999999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73318</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75774</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.69397</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.39325</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.56048</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5435399999999999</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.53249</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.53842</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.46633</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75612</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.37229</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.35496</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.51852</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.61754</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.6118300000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.5313099999999999</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.51362</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.57845</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.59423</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.5953200000000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.5188200000000001</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.58988</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.53331</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5786399999999999</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.50619</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47034</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.47029</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.5043500000000001</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.43016</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49987</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45715</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.63914</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54845</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.68396</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5389400000000001</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.02807</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77368</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74139</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27998</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34144</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71804</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.64151</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34806</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99486</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59183</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49317</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.53931</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.58984</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73351</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.1771</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.6911</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.9126000000000001</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6648500000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93424</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.88064</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74496</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71425</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17552</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.1767</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.4253</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23645</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.61666</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20497</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28282</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07733</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.39906</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03321</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.66974</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.6401699999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.13962</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.63358</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47318</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45213</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48294</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.4050299999999999</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5255299999999999</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53195</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80072</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.66855</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50855</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.06812</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66681</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66332</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.7959700000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04913</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.1674</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49947</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.1923</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54601</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15332</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55672</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45932</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51128</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.53835</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.5971900000000001</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7564</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12764</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.68996</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.5549299999999999</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45921</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43183</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.4931</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45498</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44763</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58068</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47762</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44801</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46206</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46315</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5454600000000001</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45966</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46763</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.49514</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.47872</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48342</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50142</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.46309</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.37012</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.86281</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.48551</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43833</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23339</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11208</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.6998799999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17384</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09888</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.6885</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.55887</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49182</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.49656</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41326</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80223</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46576</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48437</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09326</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.3661</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.84977</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.80741</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52173</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7532300000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75186</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51191</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55424</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44194</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.51142</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.74515</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.5738799999999999</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.79735</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.75307</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40924</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.5227999999999999</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28681</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.29018</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21735</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06162</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9545</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.2846</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.61126</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49135</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.57547</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7498899999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54596</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.54122</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21409</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75287</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75127</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5752200000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44817</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49182</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.98568</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7595700000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61842</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7504299999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17298</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60081</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.72727</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.6242799999999999</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.23675</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.87366</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.8591</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.88058</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.8991699999999999</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15307</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9318200000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.67903</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9568300000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.62002</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.63815</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.73599</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.6205</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79266</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24398</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03411</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.0084</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51478</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.34103</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04814</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75399</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34524</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55683</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8012899999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5497300000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75095</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75274</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5590499999999999</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62763</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59037</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.55649</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.53743</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44801</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47348</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49464</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5571799999999999</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81147</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.15379</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.1193</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03221</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12202</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72591</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.72066</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04304</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06142</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.66852</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55545</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56192</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5499400000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47724</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46457</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5464</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5513899999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54115</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65716</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54176</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04339</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.65418</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54667</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49702</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49755</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48056</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49755</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48034</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57478</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55506</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55857</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49597</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51164</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49841</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.55841</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.65712</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15257</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.05554</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.65834</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.57996</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15095</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8636200000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6576000000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.14042</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.8131499999999999</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49245</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.50964</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49715</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53286</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34434</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.71189</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.58196</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.5885499999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.72824</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5516799999999999</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6257999999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5834400000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.62973</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00492</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17523</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92435</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.96151</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.01046</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.95156</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.91792</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.94782</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.93172</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.91508</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9174099999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.67199</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.02685</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.66939</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.02373</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.12546</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10732</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.69916</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.92202</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.84288</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.90977</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.5418</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66697</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68945</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73785</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78792</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.19699</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.0771</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.01661</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32918</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01227</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11134</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91573</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.75179</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.7510399999999999</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.81341</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69189</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69068</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55638</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.68836</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.72475</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6850700000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.74707</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6951799999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46103</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.73321</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.51976</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43938</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.9946699999999999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.89177</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00795</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.89659</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01577</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.99879</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.16536</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06802</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.09198</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.6656799999999999</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.59582</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71812</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7051799999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02564</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69811</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.75113</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13496</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.23194</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.43308</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.20163</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.36373</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.98534</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.40162</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.38089</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.74452</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.65524</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.42274</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.42455</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80751</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7553200000000001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.56063</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75412</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.81099</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31351</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00397</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9340900000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9603200000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16261</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06217</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8643200000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69343</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22292</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20879</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.20946</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15182</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.8675900000000001</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7035399999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09719</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10811</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10814</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13448</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10584</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52061</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20115</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.6403300000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57775</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.7317400000000001</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.66389</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18518</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.86213</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06613</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03323</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.05081</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03636</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06916</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12816</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05063</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06124</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18421</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16277</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21645</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20336</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26698</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16945</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14373</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12004</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10068</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12682</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17654</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19412</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.1747</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07755</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.67431</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6147899999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.56587</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.54844</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44885</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53113</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31362</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31083</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06776</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51985</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44399</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43419</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.43106</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43354</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.44198</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43864</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84835</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.56675</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.6841900000000001</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.6998300000000001</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.65147</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.9416599999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7526799999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.94702</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15878</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30678</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44601</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43411</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45942</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54624</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.25261</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.8512000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.62066</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73351</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7006100000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50281</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84433</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.86682</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.21542</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77328</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57994</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.6275299999999999</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.70799</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.5836699999999999</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7355900000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.61054</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.20022</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17678</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41146</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17817</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17886</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18417</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10415</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07888</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20743</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10656</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19286</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05149</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08297</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08314</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.5426</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.8074600000000001</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8041</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5640299999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21399</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84911</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84961</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5545599999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56257</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539400000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5477799999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5204500000000001</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55757</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17562</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8829900000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49392</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.1719</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.5094</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5694600000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8442000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7951900000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59699</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85287</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50105</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5228700000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54375</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17761</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70098</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5553400000000001</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17403</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54923</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55035</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58077</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.7996</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55506</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79908</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8490800000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17421</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79867</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6835399999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05267</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17605</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.1775</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17543</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82414</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73258</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64539</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6769299999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6849500000000001</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73121</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83477</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81799</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.61549</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8069700000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75664</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.1369</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.75117</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60945</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.6367200000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6386000000000001</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6173200000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61461</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.70414</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67086</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.81409</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70408</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
